--- a/data/trans_orig/IMC_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2007</t>
+          <t>Población con sobrepeso u obesidad en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>412267</t>
+          <t>409117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>460950</t>
+          <t>460166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>328989</t>
+          <t>329822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>377929</t>
+          <t>380976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>755522</t>
+          <t>755123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>827687</t>
+          <t>828122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>228375</t>
+          <t>229159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277058</t>
+          <t>280208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301127</t>
+          <t>298080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>350067</t>
+          <t>349234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540693</t>
+          <t>540258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>612858</t>
+          <t>613257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>560810</t>
+          <t>557452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>621553</t>
+          <t>623450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>442877</t>
+          <t>443250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>504115</t>
+          <t>505959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1025919</t>
+          <t>1026479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1113541</t>
+          <t>1110804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332157</t>
+          <t>330260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392900</t>
+          <t>396258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451578</t>
+          <t>449734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512816</t>
+          <t>512443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>795862</t>
+          <t>798599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883484</t>
+          <t>882924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>348950</t>
+          <t>350151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>402309</t>
+          <t>402388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>284413</t>
+          <t>286373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>334563</t>
+          <t>336944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>648852</t>
+          <t>650100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722330</t>
+          <t>726726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269812</t>
+          <t>269733</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323171</t>
+          <t>321970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>342606</t>
+          <t>340225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>392756</t>
+          <t>390796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626960</t>
+          <t>622564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>700438</t>
+          <t>699190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>490836</t>
+          <t>490184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>552473</t>
+          <t>548546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>405671</t>
+          <t>406344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>468385</t>
+          <t>468224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>906832</t>
+          <t>910223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>998087</t>
+          <t>1000743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>376450</t>
+          <t>380377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>438087</t>
+          <t>438739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>552676</t>
+          <t>552837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615390</t>
+          <t>614717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>951897</t>
+          <t>949241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1043152</t>
+          <t>1039761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1870667</t>
+          <t>1866586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1980387</t>
+          <t>1979827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1514167</t>
+          <t>1515368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1636648</t>
+          <t>1632779</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3408281</t>
+          <t>3418548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3574539</t>
+          <t>3579984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1263692</t>
+          <t>1264252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1373412</t>
+          <t>1377493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1696330</t>
+          <t>1700199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1818811</t>
+          <t>1817610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3002518</t>
+          <t>2997073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3168776</t>
+          <t>3158509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2012</t>
+          <t>Población con sobrepeso u obesidad en 2012 (tasa de respuesta: 96,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>464235</t>
+          <t>464377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>512518</t>
+          <t>513646</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>335342</t>
+          <t>337816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>388872</t>
+          <t>389869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>816717</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>886135</t>
+          <t>891366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181096</t>
+          <t>179968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229379</t>
+          <t>229237</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273291</t>
+          <t>272294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326821</t>
+          <t>324347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>469642</t>
+          <t>464411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539060</t>
+          <t>539391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>626192</t>
+          <t>621591</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>684766</t>
+          <t>686079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>520598</t>
+          <t>519347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>583906</t>
+          <t>583791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1162070</t>
+          <t>1163427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1254090</t>
+          <t>1257360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,48%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>307072</t>
+          <t>305759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365646</t>
+          <t>370247</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405073</t>
+          <t>405188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>468381</t>
+          <t>469632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726726</t>
+          <t>723456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818746</t>
+          <t>817389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>417910</t>
+          <t>415022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>473280</t>
+          <t>472188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>393484</t>
+          <t>394012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>450476</t>
+          <t>450872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>826714</t>
+          <t>820670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>904231</t>
+          <t>903136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>266664</t>
+          <t>267756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322034</t>
+          <t>324922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295125</t>
+          <t>294729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>352117</t>
+          <t>351589</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>581314</t>
+          <t>582409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658831</t>
+          <t>664875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>582356</t>
+          <t>583299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>637736</t>
+          <t>641167</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>482956</t>
+          <t>482257</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>547580</t>
+          <t>545675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1078652</t>
+          <t>1080018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1168159</t>
+          <t>1169885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297209</t>
+          <t>293778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352589</t>
+          <t>351646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463219</t>
+          <t>465124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>527843</t>
+          <t>528542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>777584</t>
+          <t>775858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>867091</t>
+          <t>865725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2139359</t>
+          <t>2139579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2254473</t>
+          <t>2253686</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1791319</t>
+          <t>1790187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1908600</t>
+          <t>1912198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3964416</t>
+          <t>3972883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4131460</t>
+          <t>4136184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1105867</t>
+          <t>1106654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1220981</t>
+          <t>1220761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1498942</t>
+          <t>1495344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1616223</t>
+          <t>1617355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2636422</t>
+          <t>2631698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2803466</t>
+          <t>2794999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2016</t>
+          <t>Población con sobrepeso u obesidad en 2016 (tasa de respuesta: 95,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>390550</t>
+          <t>388426</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>438382</t>
+          <t>438732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>311414</t>
+          <t>310774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>360758</t>
+          <t>359406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>717033</t>
+          <t>716375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>782742</t>
+          <t>785458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199969</t>
+          <t>199619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247801</t>
+          <t>249925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255065</t>
+          <t>256417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304409</t>
+          <t>305049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>471432</t>
+          <t>468716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537141</t>
+          <t>537799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>555415</t>
+          <t>554439</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>616785</t>
+          <t>616344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>524533</t>
+          <t>521421</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>584342</t>
+          <t>587104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1094923</t>
+          <t>1095795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1187609</t>
+          <t>1189186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,11%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367468</t>
+          <t>367909</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>428838</t>
+          <t>429814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>409873</t>
+          <t>407111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469682</t>
+          <t>472794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>790859</t>
+          <t>789282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883545</t>
+          <t>882673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>415124</t>
+          <t>414847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>470278</t>
+          <t>469292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>322334</t>
+          <t>327622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>380080</t>
+          <t>383547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>752886</t>
+          <t>759381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>834296</t>
+          <t>838428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275277</t>
+          <t>276263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330431</t>
+          <t>330708</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367419</t>
+          <t>363952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425165</t>
+          <t>419877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658758</t>
+          <t>654626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>740168</t>
+          <t>733673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,14%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>514022</t>
+          <t>510861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>574318</t>
+          <t>572743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>471185</t>
+          <t>471819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>537317</t>
+          <t>536831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1002563</t>
+          <t>997158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1089026</t>
+          <t>1089164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331439</t>
+          <t>333014</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>391735</t>
+          <t>394896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447474</t>
+          <t>447960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513606</t>
+          <t>512972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>801522</t>
+          <t>801384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>887985</t>
+          <t>893390</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1935748</t>
+          <t>1932044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2047170</t>
+          <t>2043113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1690039</t>
+          <t>1687084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1806197</t>
+          <t>1809568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3656367</t>
+          <t>3644058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3817441</t>
+          <t>3813354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1226746</t>
+          <t>1230803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1338168</t>
+          <t>1341872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1536131</t>
+          <t>1532760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1652289</t>
+          <t>1655244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2798803</t>
+          <t>2802890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2959877</t>
+          <t>2972186</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2023</t>
+          <t>Población con sobrepeso u obesidad en 2023 (tasa de respuesta: 96,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>400493</t>
+          <t>401234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>452224</t>
+          <t>452516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>342061</t>
+          <t>340965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383734</t>
+          <t>384098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>756977</t>
+          <t>754845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>823574</t>
+          <t>823550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168316</t>
+          <t>168024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220047</t>
+          <t>219306</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261383</t>
+          <t>261019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303056</t>
+          <t>304152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>442083</t>
+          <t>442107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>508680</t>
+          <t>510812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>673639</t>
+          <t>680262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>963710</t>
+          <t>989692</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446791</t>
+          <t>447915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>498176</t>
+          <t>499819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1144439</t>
+          <t>1138808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1529463</t>
+          <t>1550703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218463</t>
+          <t>192481</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508534</t>
+          <t>501911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429370</t>
+          <t>427727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480755</t>
+          <t>479631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>580256</t>
+          <t>559016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>965280</t>
+          <t>970911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>398569</t>
+          <t>400178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>459010</t>
+          <t>462901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>420258</t>
+          <t>421811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>714432</t>
+          <t>697261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>859285</t>
+          <t>860281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1188516</t>
+          <t>1186292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,32%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237868</t>
+          <t>233977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298309</t>
+          <t>296700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163635</t>
+          <t>180806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457809</t>
+          <t>456256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>386429</t>
+          <t>388653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>715660</t>
+          <t>714664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>525503</t>
+          <t>522771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>589063</t>
+          <t>591394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>513760</t>
+          <t>512695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>665986</t>
+          <t>659992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1060327</t>
+          <t>1061949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1208715</t>
+          <t>1211520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>309584</t>
+          <t>307253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373144</t>
+          <t>375876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>383462</t>
+          <t>389456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>535688</t>
+          <t>536753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739381</t>
+          <t>736576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>887769</t>
+          <t>886147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2087287</t>
+          <t>2088119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2493642</t>
+          <t>2474728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1795803</t>
+          <t>1806140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2223087</t>
+          <t>2215162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3939613</t>
+          <t>3946098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4497479</t>
+          <t>4540917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>904596</t>
+          <t>923510</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1310951</t>
+          <t>1310119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1277091</t>
+          <t>1285016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1704375</t>
+          <t>1694038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2400937</t>
+          <t>2357499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2958803</t>
+          <t>2952318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>409117</t>
+          <t>408311</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>460166</t>
+          <t>459396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>329822</t>
+          <t>328379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>380976</t>
+          <t>379900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>755123</t>
+          <t>752918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>828122</t>
+          <t>825751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229159</t>
+          <t>229929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280208</t>
+          <t>281014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298080</t>
+          <t>299156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>349234</t>
+          <t>350677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540258</t>
+          <t>542629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>613257</t>
+          <t>615462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>557452</t>
+          <t>562050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>623450</t>
+          <t>624994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>443250</t>
+          <t>442440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>505959</t>
+          <t>503719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1026479</t>
+          <t>1016439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1110804</t>
+          <t>1109894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330260</t>
+          <t>328716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>396258</t>
+          <t>391660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449734</t>
+          <t>451974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512443</t>
+          <t>513253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>798599</t>
+          <t>799509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>882924</t>
+          <t>892964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>350151</t>
+          <t>347877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>402388</t>
+          <t>402979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>286373</t>
+          <t>287570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>336944</t>
+          <t>337160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>650100</t>
+          <t>647415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>726726</t>
+          <t>721580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269733</t>
+          <t>269142</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321970</t>
+          <t>324244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>340225</t>
+          <t>340009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>390796</t>
+          <t>389599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622564</t>
+          <t>627710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>699190</t>
+          <t>701875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>490184</t>
+          <t>488221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>548546</t>
+          <t>549320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>406344</t>
+          <t>401810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>468224</t>
+          <t>465358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>910223</t>
+          <t>911052</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1000743</t>
+          <t>999548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>380377</t>
+          <t>379603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>438739</t>
+          <t>440702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>552837</t>
+          <t>555703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>614717</t>
+          <t>619251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>949241</t>
+          <t>950436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1039761</t>
+          <t>1038932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1866586</t>
+          <t>1869898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1979827</t>
+          <t>1981608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1515368</t>
+          <t>1519462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1632779</t>
+          <t>1631473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3418548</t>
+          <t>3422415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3579984</t>
+          <t>3589263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1264252</t>
+          <t>1262471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1377493</t>
+          <t>1374181</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1700199</t>
+          <t>1701505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1817610</t>
+          <t>1813516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2997073</t>
+          <t>2987794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3158509</t>
+          <t>3154642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>464377</t>
+          <t>464465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>513646</t>
+          <t>513290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>337816</t>
+          <t>333734</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>389869</t>
+          <t>388324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>811075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>891366</t>
+          <t>883100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>179968</t>
+          <t>180324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229237</t>
+          <t>229149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272294</t>
+          <t>273839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>324347</t>
+          <t>328429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>464411</t>
+          <t>472677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539391</t>
+          <t>544702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>621591</t>
+          <t>624487</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>686079</t>
+          <t>685774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>519347</t>
+          <t>519006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>583791</t>
+          <t>584344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1163427</t>
+          <t>1162112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1257360</t>
+          <t>1255725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>305759</t>
+          <t>306064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370247</t>
+          <t>367351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405188</t>
+          <t>404635</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469632</t>
+          <t>469973</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>723456</t>
+          <t>725091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>817389</t>
+          <t>818704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>415022</t>
+          <t>412904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>472188</t>
+          <t>470387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>394012</t>
+          <t>391483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>450872</t>
+          <t>449513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>820670</t>
+          <t>825558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>903136</t>
+          <t>904364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267756</t>
+          <t>269557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324922</t>
+          <t>327040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294729</t>
+          <t>296088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>351589</t>
+          <t>354118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>582409</t>
+          <t>581181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664875</t>
+          <t>659987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>583299</t>
+          <t>580554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>641167</t>
+          <t>637682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>482257</t>
+          <t>483050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>545675</t>
+          <t>546356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1080018</t>
+          <t>1080139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1169885</t>
+          <t>1169016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293778</t>
+          <t>297263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351646</t>
+          <t>354391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>465124</t>
+          <t>464443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>528542</t>
+          <t>527749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>775858</t>
+          <t>776727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>865725</t>
+          <t>865604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2139579</t>
+          <t>2142227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2253686</t>
+          <t>2257017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1790187</t>
+          <t>1792324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1912198</t>
+          <t>1914143</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3972883</t>
+          <t>3960643</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4136184</t>
+          <t>4128547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,0%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1106654</t>
+          <t>1103323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1220761</t>
+          <t>1218113</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1495344</t>
+          <t>1493399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1617355</t>
+          <t>1615218</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2631698</t>
+          <t>2639335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2794999</t>
+          <t>2807239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>388426</t>
+          <t>390464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>438732</t>
+          <t>438770</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>310774</t>
+          <t>311151</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>359406</t>
+          <t>359430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>716375</t>
+          <t>716351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>785458</t>
+          <t>781699</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199619</t>
+          <t>199581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249925</t>
+          <t>247887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256417</t>
+          <t>256393</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305049</t>
+          <t>304672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>468716</t>
+          <t>472475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537799</t>
+          <t>537823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>554439</t>
+          <t>557460</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>616344</t>
+          <t>617934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>521421</t>
+          <t>523613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>587104</t>
+          <t>584002</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1095795</t>
+          <t>1096840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1189186</t>
+          <t>1186138</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367909</t>
+          <t>366319</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>429814</t>
+          <t>426793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>407111</t>
+          <t>410213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>472794</t>
+          <t>470602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>789282</t>
+          <t>792330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>882673</t>
+          <t>881628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>414847</t>
+          <t>412877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>469292</t>
+          <t>469980</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>327622</t>
+          <t>326145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>383547</t>
+          <t>382511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>759381</t>
+          <t>758804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>838428</t>
+          <t>835952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276263</t>
+          <t>275575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330708</t>
+          <t>332678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>363952</t>
+          <t>364988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>419877</t>
+          <t>421354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654626</t>
+          <t>657102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>733673</t>
+          <t>734250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>510861</t>
+          <t>514937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>572743</t>
+          <t>575999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>471819</t>
+          <t>468499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>536831</t>
+          <t>531819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>997158</t>
+          <t>1007746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1089164</t>
+          <t>1093009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333014</t>
+          <t>329758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>394896</t>
+          <t>390820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447960</t>
+          <t>452972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512972</t>
+          <t>516292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>801384</t>
+          <t>797539</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>893390</t>
+          <t>882802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1932044</t>
+          <t>1929506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2043113</t>
+          <t>2045342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1687084</t>
+          <t>1687468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1809568</t>
+          <t>1800615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3644058</t>
+          <t>3651727</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3813354</t>
+          <t>3812538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1230803</t>
+          <t>1228574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1341872</t>
+          <t>1344410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1532760</t>
+          <t>1541713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1655244</t>
+          <t>1654860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2802890</t>
+          <t>2803706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2972186</t>
+          <t>2964517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>427462</t>
+          <t>451616</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>401234</t>
+          <t>426072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>452516</t>
+          <t>476319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>362505</t>
+          <t>390210</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>340965</t>
+          <t>366601</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>384098</t>
+          <t>412222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>789967</t>
+          <t>841826</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>754845</t>
+          <t>806504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>823550</t>
+          <t>877315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>193078</t>
+          <t>216395</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168024</t>
+          <t>191692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>219306</t>
+          <t>241939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>282612</t>
+          <t>306986</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261019</t>
+          <t>284974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304152</t>
+          <t>330595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>475690</t>
+          <t>523381</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>442107</t>
+          <t>487892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510812</t>
+          <t>558703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>620540</t>
+          <t>668011</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>620540</t>
+          <t>668011</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>620540</t>
+          <t>668011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>645117</t>
+          <t>697196</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>645117</t>
+          <t>697196</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>645117</t>
+          <t>697196</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265657</t>
+          <t>1365207</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265657</t>
+          <t>1365207</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265657</t>
+          <t>1365207</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>791776</t>
+          <t>605823</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>680262</t>
+          <t>566076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>989692</t>
+          <t>639903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>473813</t>
+          <t>535958</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447915</t>
+          <t>506114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>499819</t>
+          <t>564210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1265589</t>
+          <t>1141781</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1138808</t>
+          <t>1095722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1550703</t>
+          <t>1192708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>390397</t>
+          <t>431708</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>192481</t>
+          <t>397628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501911</t>
+          <t>471455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>453733</t>
+          <t>501493</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427727</t>
+          <t>473241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479631</t>
+          <t>531337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>844130</t>
+          <t>933201</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>559016</t>
+          <t>882274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970911</t>
+          <t>979260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1182173</t>
+          <t>1037531</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1182173</t>
+          <t>1037531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1182173</t>
+          <t>1037531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>927546</t>
+          <t>1037451</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>927546</t>
+          <t>1037451</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>927546</t>
+          <t>1037451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109719</t>
+          <t>2074982</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109719</t>
+          <t>2074982</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109719</t>
+          <t>2074982</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>432510</t>
+          <t>495388</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>400178</t>
+          <t>464878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>462901</t>
+          <t>526327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>534265</t>
+          <t>391025</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>421811</t>
+          <t>365885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>697261</t>
+          <t>418599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>966776</t>
+          <t>886412</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>860281</t>
+          <t>844934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1186292</t>
+          <t>927853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>264368</t>
+          <t>292755</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233977</t>
+          <t>261816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296700</t>
+          <t>323265</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>343802</t>
+          <t>396537</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180806</t>
+          <t>368963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456256</t>
+          <t>421677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>608169</t>
+          <t>689293</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>388653</t>
+          <t>647852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>714664</t>
+          <t>730771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>696878</t>
+          <t>788143</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>696878</t>
+          <t>788143</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>696878</t>
+          <t>788143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>878067</t>
+          <t>787562</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>878067</t>
+          <t>787562</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>878067</t>
+          <t>787562</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1574945</t>
+          <t>1575705</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1574945</t>
+          <t>1575705</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1574945</t>
+          <t>1575705</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>556334</t>
+          <t>585544</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>522771</t>
+          <t>551085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>591394</t>
+          <t>617935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>558436</t>
+          <t>537062</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>512695</t>
+          <t>509618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>659992</t>
+          <t>566326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1114771</t>
+          <t>1122606</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1061949</t>
+          <t>1079271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1211520</t>
+          <t>1167263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>342313</t>
+          <t>373086</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307253</t>
+          <t>340695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>375876</t>
+          <t>407545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>491012</t>
+          <t>533015</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>389456</t>
+          <t>503751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>536753</t>
+          <t>560459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>833325</t>
+          <t>906101</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>736576</t>
+          <t>861444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>886147</t>
+          <t>949436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>898647</t>
+          <t>958630</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>898647</t>
+          <t>958630</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>898647</t>
+          <t>958630</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1049448</t>
+          <t>1070077</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1049448</t>
+          <t>1070077</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1049448</t>
+          <t>1070077</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1948096</t>
+          <t>2028707</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1948096</t>
+          <t>2028707</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1948096</t>
+          <t>2028707</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2208083</t>
+          <t>2138371</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2088119</t>
+          <t>2075818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2474728</t>
+          <t>2201794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1929019</t>
+          <t>1854255</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1806140</t>
+          <t>1798777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2215162</t>
+          <t>1905633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4137102</t>
+          <t>3992626</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3946098</t>
+          <t>3911796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4540917</t>
+          <t>4078433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1190155</t>
+          <t>1313944</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>923510</t>
+          <t>1250521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1310119</t>
+          <t>1376497</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1571159</t>
+          <t>1738031</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1285016</t>
+          <t>1686653</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1694038</t>
+          <t>1793509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2761314</t>
+          <t>3051975</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2357499</t>
+          <t>2966168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2952318</t>
+          <t>3132805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
